--- a/database/event/6586/event_6586_evp_summary.xlsx
+++ b/database/event/6586/event_6586_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.136100000000001</v>
+        <v>8.4299</v>
       </c>
       <c r="C2" t="n">
-        <v>4.3193</v>
+        <v>4.4753</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8654</v>
+        <v>2.9146</v>
       </c>
       <c r="E2" t="n">
-        <v>8.136100000000001</v>
+        <v>8.4299</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4079</v>
+        <v>3.7017</v>
       </c>
       <c r="G2" t="n">
         <v>4.7282</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4079</v>
+        <v>3.7017</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4079</v>
+        <v>3.7017</v>
       </c>
       <c r="J2" t="n">
         <v>4.7282</v>
@@ -529,7 +529,7 @@
         <v>179</v>
       </c>
       <c r="M2" t="n">
-        <v>8.136100000000001</v>
+        <v>8.4299</v>
       </c>
       <c r="N2" t="n">
         <v>314</v>
@@ -548,7 +548,7 @@
         <v>4.2433</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8076</v>
+        <v>2.7405</v>
       </c>
       <c r="E3" t="n">
         <v>7.993</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.7723</v>
+        <v>7.0627</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5953</v>
+        <v>3.7495</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3145</v>
+        <v>2.3699</v>
       </c>
       <c r="E4" t="n">
-        <v>6.7723</v>
+        <v>7.0627</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9786</v>
+        <v>2.998</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7937</v>
+        <v>4.0647</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9786</v>
+        <v>2.998</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9786</v>
+        <v>2.998</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7937</v>
+        <v>4.0647</v>
       </c>
       <c r="K4" t="n">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="L4" t="n">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="M4" t="n">
-        <v>6.7723</v>
+        <v>7.0627</v>
       </c>
       <c r="N4" t="n">
-        <v>314</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3414</v>
+        <v>6.957</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3665</v>
+        <v>3.6933</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1404</v>
+        <v>2.3278</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3414</v>
+        <v>6.957</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2766</v>
+        <v>2.1633</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0647</v>
+        <v>4.7937</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2766</v>
+        <v>2.1633</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2766</v>
+        <v>2.1633</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0647</v>
+        <v>4.7937</v>
       </c>
       <c r="K5" t="n">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="L5" t="n">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="M5" t="n">
-        <v>6.3413</v>
+        <v>6.957000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>259</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6">
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7062</v>
+        <v>5.637</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4984</v>
+        <v>2.9926</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4798</v>
+        <v>1.8019</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7062</v>
+        <v>5.637</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8499</v>
+        <v>3.7807</v>
       </c>
       <c r="G6" t="n">
         <v>1.8563</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8499</v>
+        <v>3.7807</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8499</v>
+        <v>3.7807</v>
       </c>
       <c r="J6" t="n">
         <v>1.8563</v>
@@ -713,7 +713,7 @@
         <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7062</v>
+        <v>5.637</v>
       </c>
       <c r="N6" t="n">
         <v>359</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3671</v>
+        <v>5.2376</v>
       </c>
       <c r="C7" t="n">
-        <v>2.3184</v>
+        <v>2.7806</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3428</v>
+        <v>1.6428</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3671</v>
+        <v>5.2376</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0085</v>
+        <v>2.879</v>
       </c>
       <c r="G7" t="n">
         <v>2.3586</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0085</v>
+        <v>2.879</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0085</v>
+        <v>2.879</v>
       </c>
       <c r="J7" t="n">
         <v>2.3586</v>
@@ -759,7 +759,7 @@
         <v>182</v>
       </c>
       <c r="M7" t="n">
-        <v>4.367100000000001</v>
+        <v>5.2376</v>
       </c>
       <c r="N7" t="n">
         <v>347</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2401</v>
+        <v>4.7192</v>
       </c>
       <c r="C8" t="n">
-        <v>2.251</v>
+        <v>2.5053</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2915</v>
+        <v>1.4362</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2401</v>
+        <v>4.7192</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2968</v>
+        <v>3.7759</v>
       </c>
       <c r="G8" t="n">
         <v>0.9433</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2968</v>
+        <v>3.7759</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3121</v>
+        <v>3.8077</v>
       </c>
       <c r="J8" t="n">
         <v>0.9433</v>
@@ -805,7 +805,7 @@
         <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2554</v>
+        <v>4.751</v>
       </c>
       <c r="N8" t="n">
         <v>269</v>
@@ -824,7 +824,7 @@
         <v>2.0088</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1072</v>
+        <v>1.0636</v>
       </c>
       <c r="E9" t="n">
         <v>3.7839</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3316</v>
+        <v>3.3206</v>
       </c>
       <c r="C10" t="n">
-        <v>1.7687</v>
+        <v>1.7628</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9245</v>
+        <v>0.879</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3316</v>
+        <v>3.3206</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9552</v>
+        <v>2.9442</v>
       </c>
       <c r="G10" t="n">
         <v>0.3764</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9552</v>
+        <v>2.9442</v>
       </c>
       <c r="I10" t="n">
         <v>2.969</v>
@@ -906,323 +906,323 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1925</v>
+        <v>3.2211</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6948</v>
+        <v>1.71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8683</v>
+        <v>0.8394</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1925</v>
+        <v>3.2211</v>
       </c>
       <c r="F11" t="n">
-        <v>3.422</v>
+        <v>3.997</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2295</v>
+        <v>-0.7759</v>
       </c>
       <c r="H11" t="n">
-        <v>3.422</v>
+        <v>3.997</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4379</v>
+        <v>4.0307</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2295</v>
+        <v>-0.7759</v>
       </c>
       <c r="K11" t="n">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2084</v>
+        <v>3.2548</v>
       </c>
       <c r="N11" t="n">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0389</v>
+        <v>3.1797</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6133</v>
+        <v>1.688</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8063</v>
+        <v>0.8229</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0389</v>
+        <v>3.1797</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8148</v>
+        <v>3.4092</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7759</v>
+        <v>-0.2295</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8148</v>
+        <v>3.4092</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8326</v>
+        <v>3.4379</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7759</v>
+        <v>-0.2295</v>
       </c>
       <c r="K12" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L12" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0567</v>
+        <v>3.2084</v>
       </c>
       <c r="N12" t="n">
-        <v>287</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Zyphon</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6206</v>
+        <v>2.9207</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3912</v>
+        <v>1.5505</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6373</v>
+        <v>0.7197</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6206</v>
+        <v>2.9207</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6206</v>
+        <v>0.2843</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2.6365</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6206</v>
+        <v>0.2843</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6206</v>
+        <v>0.2843</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2.6365</v>
       </c>
       <c r="K13" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6206</v>
+        <v>2.9208</v>
       </c>
       <c r="N13" t="n">
-        <v>154</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4435</v>
+        <v>2.6429</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2972</v>
+        <v>1.4031</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5658</v>
+        <v>0.609</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4435</v>
+        <v>2.6429</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6278</v>
+        <v>2.966</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1843</v>
+        <v>-0.3231</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6278</v>
+        <v>2.966</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6401</v>
+        <v>2.966</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1843</v>
+        <v>-0.3231</v>
       </c>
       <c r="K14" t="n">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="L14" t="n">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4558</v>
+        <v>2.6429</v>
       </c>
       <c r="N14" t="n">
-        <v>287</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>Zyphon</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1572</v>
+        <v>2.6206</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1452</v>
+        <v>1.3912</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4501</v>
+        <v>0.6001</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1572</v>
+        <v>2.6206</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1572</v>
+        <v>2.6206</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1572</v>
+        <v>2.6206</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1572</v>
+        <v>2.6206</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1572</v>
+        <v>2.6206</v>
       </c>
       <c r="N15" t="n">
-        <v>200</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0612</v>
+        <v>2.4793</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0943</v>
+        <v>1.3162</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4113</v>
+        <v>0.5438</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0612</v>
+        <v>2.4793</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5753</v>
+        <v>2.4793</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6365</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5753</v>
+        <v>2.4793</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5753</v>
+        <v>2.4793</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6365</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="L16" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0612</v>
+        <v>2.4793</v>
       </c>
       <c r="N16" t="n">
-        <v>347</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Patsi</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0152</v>
+        <v>2.4337</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0698</v>
+        <v>1.292</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3927</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0152</v>
+        <v>2.4337</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2517</v>
+        <v>2.618</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2365</v>
+        <v>-0.1843</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2517</v>
+        <v>2.618</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2622</v>
+        <v>2.6401</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2365</v>
+        <v>-0.1843</v>
       </c>
       <c r="K17" t="n">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="L17" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0257</v>
+        <v>2.4558</v>
       </c>
       <c r="N17" t="n">
-        <v>269</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9745</v>
+        <v>2.2861</v>
       </c>
       <c r="C18" t="n">
-        <v>1.0482</v>
+        <v>1.2137</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3763</v>
+        <v>0.4669</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9745</v>
+        <v>2.2861</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1612</v>
+        <v>2.4728</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1867</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1612</v>
+        <v>2.4728</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1712</v>
+        <v>2.4936</v>
       </c>
       <c r="J18" t="n">
         <v>-0.1867</v>
@@ -1265,7 +1265,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9845</v>
+        <v>2.3069</v>
       </c>
       <c r="N18" t="n">
         <v>269</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9595</v>
+        <v>2.1649</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0403</v>
+        <v>1.1493</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3702</v>
+        <v>0.4186</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9595</v>
+        <v>2.1649</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0657</v>
+        <v>1.2711</v>
       </c>
       <c r="G19" t="n">
         <v>0.8938</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0657</v>
+        <v>1.2711</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0657</v>
+        <v>1.2711</v>
       </c>
       <c r="J19" t="n">
         <v>0.8938</v>
@@ -1311,7 +1311,7 @@
         <v>161</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9595</v>
+        <v>2.1649</v>
       </c>
       <c r="N19" t="n">
         <v>259</v>
@@ -1320,403 +1320,403 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Patsi</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8534</v>
+        <v>2.0548</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9839</v>
+        <v>1.0909</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3274</v>
+        <v>0.3747</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8534</v>
+        <v>2.0548</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1765</v>
+        <v>2.2913</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3231</v>
+        <v>-0.2365</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1765</v>
+        <v>2.2913</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1765</v>
+        <v>2.3106</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3231</v>
+        <v>-0.2365</v>
       </c>
       <c r="K20" t="n">
-        <v>98</v>
+        <v>215</v>
       </c>
       <c r="L20" t="n">
-        <v>161</v>
+        <v>54</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8534</v>
+        <v>2.0741</v>
       </c>
       <c r="N20" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.7694</v>
+        <v>1.9789</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9393</v>
+        <v>1.0506</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2934</v>
+        <v>0.3445</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7694</v>
+        <v>1.9789</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4439</v>
+        <v>2.6644</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3255</v>
+        <v>-0.6855</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4439</v>
+        <v>2.6644</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4506</v>
+        <v>2.6644</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3255</v>
+        <v>-0.6855</v>
       </c>
       <c r="K21" t="n">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="L21" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>1.7761</v>
+        <v>1.9789</v>
       </c>
       <c r="N21" t="n">
-        <v>287</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.7143</v>
+        <v>1.9756</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9101</v>
+        <v>1.0488</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2712</v>
+        <v>0.3432</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7143</v>
+        <v>1.9756</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4726</v>
+        <v>2.4304</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2417</v>
+        <v>-0.4548</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4726</v>
+        <v>2.4304</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4726</v>
+        <v>2.4304</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2417</v>
+        <v>-0.4548</v>
       </c>
       <c r="K22" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="L22" t="n">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7143</v>
+        <v>1.9756</v>
       </c>
       <c r="N22" t="n">
-        <v>259</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7135</v>
+        <v>1.8367</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9097</v>
+        <v>0.9751</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2709</v>
+        <v>0.2878</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7135</v>
+        <v>1.8367</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7135</v>
+        <v>2.6185</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7135</v>
+        <v>2.6185</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7135</v>
+        <v>2.6185</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>224</v>
+        <v>165</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="M23" t="n">
-        <v>1.7135</v>
+        <v>1.8367</v>
       </c>
       <c r="N23" t="n">
-        <v>224</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6476</v>
+        <v>1.8258</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8747</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2442</v>
+        <v>0.2835</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6476</v>
+        <v>1.8258</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4407</v>
+        <v>1.8258</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7931</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.4407</v>
+        <v>1.8258</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4407</v>
+        <v>1.8258</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7931</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>110</v>
+        <v>224</v>
       </c>
       <c r="L24" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6476</v>
+        <v>1.8258</v>
       </c>
       <c r="N24" t="n">
-        <v>191</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.5427</v>
+        <v>1.764</v>
       </c>
       <c r="C25" t="n">
-        <v>0.819</v>
+        <v>0.9365</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2019</v>
+        <v>0.2589</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5427</v>
+        <v>1.764</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4592</v>
+        <v>1.4385</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0835</v>
+        <v>0.3255</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4592</v>
+        <v>1.4385</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4592</v>
+        <v>1.4506</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0835</v>
+        <v>0.3255</v>
       </c>
       <c r="K25" t="n">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="L25" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="M25" t="n">
-        <v>1.5427</v>
+        <v>1.7761</v>
       </c>
       <c r="N25" t="n">
-        <v>347</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.513</v>
+        <v>1.7343</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8032</v>
+        <v>0.9207</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1899</v>
+        <v>0.247</v>
       </c>
       <c r="E26" t="n">
-        <v>1.513</v>
+        <v>1.7343</v>
       </c>
       <c r="F26" t="n">
-        <v>2.1985</v>
+        <v>1.7343</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6855</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.1985</v>
+        <v>1.7343</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1985</v>
+        <v>1.7343</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6855</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="L26" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.513</v>
+        <v>1.7343</v>
       </c>
       <c r="N26" t="n">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2235</v>
+        <v>1.7143</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6495</v>
+        <v>0.9101</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.2391</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2235</v>
+        <v>1.7143</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2235</v>
+        <v>1.4726</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.2417</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2235</v>
+        <v>1.4726</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2235</v>
+        <v>1.4726</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.2417</v>
       </c>
       <c r="K27" t="n">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2235</v>
+        <v>1.7143</v>
       </c>
       <c r="N27" t="n">
-        <v>153</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.1868</v>
+        <v>1.6765</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6301</v>
+        <v>0.89</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0581</v>
+        <v>0.224</v>
       </c>
       <c r="E28" t="n">
-        <v>1.1868</v>
+        <v>1.6765</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6416</v>
+        <v>2.4696</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4548</v>
+        <v>-0.7931</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6416</v>
+        <v>2.4696</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6416</v>
+        <v>2.4696</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4548</v>
+        <v>-0.7931</v>
       </c>
       <c r="K28" t="n">
         <v>110</v>
@@ -1725,7 +1725,7 @@
         <v>81</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1868</v>
+        <v>1.6765</v>
       </c>
       <c r="N28" t="n">
         <v>191</v>
@@ -1734,35 +1734,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.1123</v>
+        <v>1.5652</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5905</v>
+        <v>0.8309</v>
       </c>
       <c r="D29" t="n">
-        <v>0.028</v>
+        <v>0.1797</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1123</v>
+        <v>1.5652</v>
       </c>
       <c r="F29" t="n">
-        <v>1.935</v>
+        <v>1.4817</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.8227</v>
+        <v>0.0835</v>
       </c>
       <c r="H29" t="n">
-        <v>1.935</v>
+        <v>1.4817</v>
       </c>
       <c r="I29" t="n">
-        <v>1.935</v>
+        <v>1.4817</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.8227</v>
+        <v>0.0835</v>
       </c>
       <c r="K29" t="n">
         <v>165</v>
@@ -1771,7 +1771,7 @@
         <v>182</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1123</v>
+        <v>1.5652</v>
       </c>
       <c r="N29" t="n">
         <v>347</v>
@@ -1780,35 +1780,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>FASHR</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0381</v>
+        <v>1.431</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5511</v>
+        <v>0.7597</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.002</v>
+        <v>0.1262</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0381</v>
+        <v>1.431</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3898</v>
+        <v>2.2747</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3517</v>
+        <v>-0.8437</v>
       </c>
       <c r="H30" t="n">
-        <v>1.3898</v>
+        <v>2.2747</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3898</v>
+        <v>2.2747</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3517</v>
+        <v>-0.8437</v>
       </c>
       <c r="K30" t="n">
         <v>123</v>
@@ -1817,7 +1817,7 @@
         <v>51</v>
       </c>
       <c r="M30" t="n">
-        <v>1.0381</v>
+        <v>1.431</v>
       </c>
       <c r="N30" t="n">
         <v>174</v>
@@ -1826,32 +1826,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.0047</v>
+        <v>1.2235</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5334</v>
+        <v>0.6495</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0155</v>
+        <v>0.0435</v>
       </c>
       <c r="E31" t="n">
-        <v>1.0047</v>
+        <v>1.2235</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0047</v>
+        <v>1.2235</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.0047</v>
+        <v>1.2235</v>
       </c>
       <c r="I31" t="n">
-        <v>1.0047</v>
+        <v>1.2235</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.0047</v>
+        <v>1.2235</v>
       </c>
       <c r="N31" t="n">
         <v>153</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.911</v>
+        <v>1.1566</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4836</v>
+        <v>0.614</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0533</v>
+        <v>0.0169</v>
       </c>
       <c r="E32" t="n">
-        <v>0.911</v>
+        <v>1.1566</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9875</v>
+        <v>1.2331</v>
       </c>
       <c r="G32" t="n">
         <v>-0.0765</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9875</v>
+        <v>1.2331</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9875</v>
+        <v>1.2331</v>
       </c>
       <c r="J32" t="n">
         <v>-0.0765</v>
@@ -1909,7 +1909,7 @@
         <v>160</v>
       </c>
       <c r="M32" t="n">
-        <v>0.911</v>
+        <v>1.1566</v>
       </c>
       <c r="N32" t="n">
         <v>359</v>
@@ -1918,308 +1918,308 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8974</v>
+        <v>1.1123</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4764</v>
+        <v>0.5905</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0588</v>
+        <v>-0.0008</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8974</v>
+        <v>1.1123</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2251</v>
+        <v>1.935</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6723</v>
+        <v>-0.8227</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2251</v>
+        <v>1.935</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2251</v>
+        <v>1.935</v>
       </c>
       <c r="J33" t="n">
-        <v>0.6723</v>
+        <v>-0.8227</v>
       </c>
       <c r="K33" t="n">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="L33" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8974</v>
+        <v>1.1123</v>
       </c>
       <c r="N33" t="n">
-        <v>314</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8655</v>
+        <v>1.067</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4595</v>
+        <v>0.5665</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0717</v>
+        <v>-0.0188</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8655</v>
+        <v>1.067</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8655</v>
+        <v>0.3947</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.6723</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8655</v>
+        <v>0.3947</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8655</v>
+        <v>0.3947</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.6723</v>
       </c>
       <c r="K34" t="n">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8655</v>
+        <v>1.067</v>
       </c>
       <c r="N34" t="n">
-        <v>166</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8478</v>
+        <v>1.0471</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4501</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0789</v>
+        <v>-0.0267</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8478</v>
+        <v>1.0471</v>
       </c>
       <c r="F35" t="n">
-        <v>1.6296</v>
+        <v>1.0471</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.7818000000000001</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.6296</v>
+        <v>1.0471</v>
       </c>
       <c r="I35" t="n">
-        <v>1.6296</v>
+        <v>1.0471</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.7818000000000001</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>165</v>
+        <v>224</v>
       </c>
       <c r="L35" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8477999999999999</v>
+        <v>1.0471</v>
       </c>
       <c r="N35" t="n">
-        <v>347</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7692</v>
+        <v>1.0381</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4084</v>
+        <v>0.5511</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1106</v>
+        <v>-0.0303</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7692</v>
+        <v>1.0381</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7692</v>
+        <v>1.3898</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.3517</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7692</v>
+        <v>1.3898</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7692</v>
+        <v>1.3898</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.3517</v>
       </c>
       <c r="K36" t="n">
-        <v>224</v>
+        <v>123</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7692</v>
+        <v>1.0381</v>
       </c>
       <c r="N36" t="n">
-        <v>224</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FASHR</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7678</v>
+        <v>1.0084</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4076</v>
+        <v>0.5353</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1112</v>
+        <v>-0.0422</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7678</v>
+        <v>1.0084</v>
       </c>
       <c r="F37" t="n">
-        <v>1.6115</v>
+        <v>1.0084</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.8437</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.6115</v>
+        <v>1.0084</v>
       </c>
       <c r="I37" t="n">
-        <v>1.6115</v>
+        <v>1.0084</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8437</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>123</v>
+        <v>205</v>
       </c>
       <c r="L37" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7677999999999999</v>
+        <v>1.0084</v>
       </c>
       <c r="N37" t="n">
-        <v>174</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.697</v>
+        <v>1.0047</v>
       </c>
       <c r="C38" t="n">
-        <v>0.37</v>
+        <v>0.5334</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1398</v>
+        <v>-0.0436</v>
       </c>
       <c r="E38" t="n">
-        <v>0.697</v>
+        <v>1.0047</v>
       </c>
       <c r="F38" t="n">
-        <v>0.697</v>
+        <v>1.0047</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.697</v>
+        <v>1.0047</v>
       </c>
       <c r="I38" t="n">
-        <v>0.697</v>
+        <v>1.0047</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.697</v>
+        <v>1.0047</v>
       </c>
       <c r="N38" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6782</v>
+        <v>0.9908</v>
       </c>
       <c r="C39" t="n">
-        <v>0.36</v>
+        <v>0.526</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1474</v>
+        <v>-0.0492</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6782</v>
+        <v>0.9908</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6782</v>
+        <v>0.9908</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6782</v>
+        <v>0.9908</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6782</v>
+        <v>0.9908</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6782</v>
+        <v>0.9908</v>
       </c>
       <c r="N39" t="n">
         <v>166</v>
@@ -2240,461 +2240,461 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6014</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3193</v>
+        <v>0.5023</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1784</v>
+        <v>-0.067</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6014</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.1339</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7353</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.1339</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1339</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7353</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>110</v>
+        <v>224</v>
       </c>
       <c r="L40" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6013999999999999</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>191</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.7503</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3144</v>
+        <v>0.3983</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1821</v>
+        <v>-0.145</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.7503</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5966</v>
+        <v>0.7503</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0044</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5966</v>
+        <v>0.7503</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5966</v>
+        <v>0.7503</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.0044</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>123</v>
+        <v>205</v>
       </c>
       <c r="L41" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5922000000000001</v>
+        <v>0.7503</v>
       </c>
       <c r="N41" t="n">
-        <v>174</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4268</v>
+        <v>0.697</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2266</v>
+        <v>0.37</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2489</v>
+        <v>-0.1662</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4268</v>
+        <v>0.697</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9067</v>
+        <v>0.697</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.4799</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9067</v>
+        <v>0.697</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9109</v>
+        <v>0.697</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.4799</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>215</v>
+        <v>154</v>
       </c>
       <c r="L42" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.431</v>
+        <v>0.697</v>
       </c>
       <c r="N42" t="n">
-        <v>269</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4207</v>
+        <v>0.6782</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2233</v>
+        <v>0.36</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2514</v>
+        <v>-0.1737</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4207</v>
+        <v>0.6782</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4207</v>
+        <v>0.6782</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4207</v>
+        <v>0.6782</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4207</v>
+        <v>0.6782</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4207</v>
+        <v>0.6782</v>
       </c>
       <c r="N43" t="n">
-        <v>205</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4183</v>
+        <v>0.6014</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2221</v>
+        <v>0.3193</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2524</v>
+        <v>-0.2043</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4183</v>
+        <v>0.6014</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4183</v>
+        <v>-0.1339</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.7353</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4183</v>
+        <v>-0.1339</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4183</v>
+        <v>-0.1339</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.7353</v>
       </c>
       <c r="K44" t="n">
-        <v>166</v>
+        <v>110</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4183</v>
+        <v>0.6013999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>166</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.39</v>
+        <v>0.5931</v>
       </c>
       <c r="C45" t="n">
-        <v>0.207</v>
+        <v>0.3149</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2638</v>
+        <v>-0.2076</v>
       </c>
       <c r="E45" t="n">
-        <v>0.39</v>
+        <v>0.5931</v>
       </c>
       <c r="F45" t="n">
-        <v>0.39</v>
+        <v>0.5975</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.0044</v>
       </c>
       <c r="H45" t="n">
-        <v>0.39</v>
+        <v>0.5975</v>
       </c>
       <c r="I45" t="n">
-        <v>0.39</v>
+        <v>0.5975</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.0044</v>
       </c>
       <c r="K45" t="n">
-        <v>224</v>
+        <v>123</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M45" t="n">
-        <v>0.39</v>
+        <v>0.5931000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>224</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>s1n</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3828</v>
+        <v>0.4639</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2032</v>
+        <v>0.2463</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2667</v>
+        <v>-0.2591</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3828</v>
+        <v>0.4639</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3828</v>
+        <v>0.4639</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3828</v>
+        <v>0.4639</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3828</v>
+        <v>0.4639</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>114</v>
+        <v>205</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3828</v>
+        <v>0.4639</v>
       </c>
       <c r="N46" t="n">
-        <v>114</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3469</v>
+        <v>0.4234</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1842</v>
+        <v>0.2248</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2812</v>
+        <v>-0.2752</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3469</v>
+        <v>0.4234</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.9033</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.459</v>
+        <v>-0.4799</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.9033</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8097</v>
+        <v>0.9109</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.459</v>
+        <v>-0.4799</v>
       </c>
       <c r="K47" t="n">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L47" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="M47" t="n">
-        <v>0.3507</v>
+        <v>0.431</v>
       </c>
       <c r="N47" t="n">
-        <v>287</v>
+        <v>269</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2177</v>
+        <v>0.3828</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1156</v>
+        <v>0.2032</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3334</v>
+        <v>-0.2914</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2177</v>
+        <v>0.3828</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2177</v>
+        <v>0.3828</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2177</v>
+        <v>0.3828</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2177</v>
+        <v>0.3828</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>200</v>
+        <v>114</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2177</v>
+        <v>0.3828</v>
       </c>
       <c r="N48" t="n">
-        <v>200</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>s1n</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1643</v>
+        <v>0.3439</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0872</v>
+        <v>0.1826</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.355</v>
+        <v>-0.3069</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1643</v>
+        <v>0.3439</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1643</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.459</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1643</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1643</v>
+        <v>0.8097</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.459</v>
       </c>
       <c r="K49" t="n">
         <v>205</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1643</v>
+        <v>0.3507</v>
       </c>
       <c r="N49" t="n">
-        <v>205</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50">
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0249</v>
+        <v>0.2881</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0132</v>
+        <v>0.1529</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4113</v>
+        <v>-0.3291</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0249</v>
+        <v>0.2881</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0035</v>
+        <v>0.2597</v>
       </c>
       <c r="G50" t="n">
         <v>0.0284</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0035</v>
+        <v>0.2597</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0035</v>
+        <v>0.2597</v>
       </c>
       <c r="J50" t="n">
         <v>0.0284</v>
@@ -2737,7 +2737,7 @@
         <v>51</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0249</v>
+        <v>0.2881</v>
       </c>
       <c r="N50" t="n">
         <v>174</v>
@@ -2746,139 +2746,139 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0163</v>
+        <v>0.2871</v>
       </c>
       <c r="C51" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.1524</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4148</v>
+        <v>-0.3295</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0163</v>
+        <v>0.2871</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0163</v>
+        <v>0.2871</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0163</v>
+        <v>0.2871</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0163</v>
+        <v>0.2871</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.0163</v>
+        <v>0.2871</v>
       </c>
       <c r="N51" t="n">
-        <v>205</v>
+        <v>224</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0067</v>
+        <v>0.2177</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0036</v>
+        <v>0.1156</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4187</v>
+        <v>-0.3572</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0067</v>
+        <v>0.2177</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3029</v>
+        <v>0.2177</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.2962</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3029</v>
+        <v>0.2177</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3029</v>
+        <v>0.2177</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.2962</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="L52" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.006699999999999984</v>
+        <v>0.2177</v>
       </c>
       <c r="N52" t="n">
-        <v>259</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0024</v>
+        <v>0.0067</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0013</v>
+        <v>0.0036</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4223</v>
+        <v>-0.4412</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0024</v>
+        <v>0.0067</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0024</v>
+        <v>0.3029</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.2962</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0024</v>
+        <v>0.3029</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0024</v>
+        <v>0.3029</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.2962</v>
       </c>
       <c r="K53" t="n">
-        <v>224</v>
+        <v>98</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.0024</v>
+        <v>0.006699999999999984</v>
       </c>
       <c r="N53" t="n">
-        <v>224</v>
+        <v>259</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.0004</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0053</v>
+        <v>0.0002</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4254</v>
+        <v>-0.4438</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.0004</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.0004</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.0004</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.0004</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.009900000000000001</v>
+        <v>0.0004</v>
       </c>
       <c r="N54" t="n">
         <v>200</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0565</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4644</v>
+        <v>-0.4863</v>
       </c>
       <c r="E55" t="n">
         <v>-0.1065</v>
@@ -2986,7 +2986,7 @@
         <v>-0.0613</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.468</v>
+        <v>-0.4899</v>
       </c>
       <c r="E56" t="n">
         <v>-0.1155</v>
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.1175</v>
+        <v>-0.1169</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0624</v>
+        <v>-0.0621</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4688</v>
+        <v>-0.4905</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.1175</v>
+        <v>-0.1169</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.5288</v>
+        <v>-0.5282</v>
       </c>
       <c r="G57" t="n">
         <v>0.4113</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.5288</v>
+        <v>-0.5282</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.5288</v>
+        <v>-0.5282</v>
       </c>
       <c r="J57" t="n">
         <v>0.4113</v>
@@ -3059,7 +3059,7 @@
         <v>160</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.1175</v>
+        <v>-0.1169</v>
       </c>
       <c r="N57" t="n">
         <v>359</v>
@@ -3068,354 +3068,354 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>juanflatroo</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.1606</v>
+        <v>-0.1256</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0853</v>
+        <v>-0.0667</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4862</v>
+        <v>-0.4939</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1606</v>
+        <v>-0.1256</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1606</v>
+        <v>1.3434</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-1.469</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.1606</v>
+        <v>1.3434</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1606</v>
+        <v>1.3434</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>-1.469</v>
       </c>
       <c r="K58" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.1606</v>
+        <v>-0.1256000000000002</v>
       </c>
       <c r="N58" t="n">
-        <v>192</v>
+        <v>359</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>juanflatroo</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.1937</v>
+        <v>-0.1606</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1028</v>
+        <v>-0.0853</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4996</v>
+        <v>-0.5079</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.1937</v>
+        <v>-0.1606</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.1937</v>
+        <v>-0.1606</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.1937</v>
+        <v>-0.1606</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1937</v>
+        <v>-0.1606</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.1937</v>
+        <v>-0.1606</v>
       </c>
       <c r="N59" t="n">
-        <v>114</v>
+        <v>192</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.2623</v>
+        <v>-0.1937</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1393</v>
+        <v>-0.1028</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5273</v>
+        <v>-0.5211</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.2623</v>
+        <v>-0.1937</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.2623</v>
+        <v>-0.1937</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.2623</v>
+        <v>-0.1937</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2623</v>
+        <v>-0.1937</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.2623</v>
+        <v>-0.1937</v>
       </c>
       <c r="N60" t="n">
-        <v>153</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.265</v>
+        <v>-0.2362</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1407</v>
+        <v>-0.1254</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5284</v>
+        <v>-0.538</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.265</v>
+        <v>-0.2362</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.265</v>
+        <v>-0.2362</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.265</v>
+        <v>-0.2362</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.265</v>
+        <v>-0.2362</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.265</v>
+        <v>-0.2362</v>
       </c>
       <c r="N61" t="n">
-        <v>114</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>sinnopsyy</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.368</v>
+        <v>-0.2623</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1954</v>
+        <v>-0.1393</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.57</v>
+        <v>-0.5484</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.368</v>
+        <v>-0.2623</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.368</v>
+        <v>-0.2623</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.368</v>
+        <v>-0.2623</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.368</v>
+        <v>-0.2623</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.368</v>
+        <v>-0.2623</v>
       </c>
       <c r="N62" t="n">
-        <v>192</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3802</v>
+        <v>-0.265</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2018</v>
+        <v>-0.1407</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.575</v>
+        <v>-0.5495</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3802</v>
+        <v>-0.265</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3802</v>
+        <v>-0.265</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3802</v>
+        <v>-0.265</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3802</v>
+        <v>-0.265</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>200</v>
+        <v>114</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3802</v>
+        <v>-0.265</v>
       </c>
       <c r="N63" t="n">
-        <v>200</v>
+        <v>114</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>sinnopsyy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3901</v>
+        <v>-0.368</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2071</v>
+        <v>-0.1954</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.579</v>
+        <v>-0.5905</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.3901</v>
+        <v>-0.368</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.3901</v>
+        <v>-0.368</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.3901</v>
+        <v>-0.368</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3901</v>
+        <v>-0.368</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.3901</v>
+        <v>-0.368</v>
       </c>
       <c r="N64" t="n">
-        <v>114</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.5496</v>
+        <v>-0.3901</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.2918</v>
+        <v>-0.2071</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6434</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5496</v>
+        <v>-0.3901</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.5496</v>
+        <v>-0.3901</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.5496</v>
+        <v>-0.3901</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5496</v>
+        <v>-0.3901</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.5496</v>
+        <v>-0.3901</v>
       </c>
       <c r="N65" t="n">
         <v>114</v>
@@ -3436,124 +3436,124 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.6694</v>
+        <v>-0.5496</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3554</v>
+        <v>-0.2918</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6918</v>
+        <v>-0.6629</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.6694</v>
+        <v>-0.5496</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.6694</v>
+        <v>-0.5496</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.6694</v>
+        <v>-0.5496</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6694</v>
+        <v>-0.5496</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.6694</v>
+        <v>-0.5496</v>
       </c>
       <c r="N66" t="n">
-        <v>166</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.9261</v>
+        <v>-0.5523</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4917</v>
+        <v>-0.2932</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7955</v>
+        <v>-0.6639</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.9261</v>
+        <v>-0.5523</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.9261</v>
+        <v>-0.5523</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.9261</v>
+        <v>-0.5523</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.9261</v>
+        <v>-0.5523</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.9261</v>
+        <v>-0.5523</v>
       </c>
       <c r="N67" t="n">
-        <v>154</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0391</v>
+        <v>-0.6694</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5516</v>
+        <v>-0.3554</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8411</v>
+        <v>-0.7106</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.0391</v>
+        <v>-0.6694</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.0391</v>
+        <v>-0.6694</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.0391</v>
+        <v>-0.6694</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.0391</v>
+        <v>-0.6694</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.0391</v>
+        <v>-0.6694</v>
       </c>
       <c r="N68" t="n">
         <v>166</v>
@@ -3574,231 +3574,231 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.0491</v>
+        <v>-0.9261</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5569</v>
+        <v>-0.4917</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8452</v>
+        <v>-0.8129</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.0491</v>
+        <v>-0.9261</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.4864</v>
+        <v>-0.9261</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4373</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.4864</v>
+        <v>-0.9261</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.4864</v>
+        <v>-0.9261</v>
       </c>
       <c r="J69" t="n">
-        <v>0.4373</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="L69" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.0491</v>
+        <v>-0.9261</v>
       </c>
       <c r="N69" t="n">
-        <v>359</v>
+        <v>154</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0563</v>
+        <v>-1.0391</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5608</v>
+        <v>-0.5516</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8481</v>
+        <v>-0.8579</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.0563</v>
+        <v>-1.0391</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4127</v>
+        <v>-1.0391</v>
       </c>
       <c r="G70" t="n">
-        <v>-1.469</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.4127</v>
+        <v>-1.0391</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4127</v>
+        <v>-1.0391</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.469</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="L70" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.0563</v>
+        <v>-1.0391</v>
       </c>
       <c r="N70" t="n">
-        <v>359</v>
+        <v>166</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.107</v>
+        <v>-1.0491</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5877</v>
+        <v>-0.5569</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8686</v>
+        <v>-0.8619</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.107</v>
+        <v>-1.0491</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.107</v>
+        <v>-1.4864</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>0.4373</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.107</v>
+        <v>-1.4864</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.107</v>
+        <v>-1.4864</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>0.4373</v>
       </c>
       <c r="K71" t="n">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.107</v>
+        <v>-1.0491</v>
       </c>
       <c r="N71" t="n">
-        <v>153</v>
+        <v>359</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>rigoN</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.1497</v>
+        <v>-1.107</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.5877</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8858</v>
+        <v>-0.8849</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.1497</v>
+        <v>-1.107</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.1497</v>
+        <v>-1.107</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.1497</v>
+        <v>-1.107</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.1497</v>
+        <v>-1.107</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.1497</v>
+        <v>-1.107</v>
       </c>
       <c r="N72" t="n">
-        <v>192</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>rigoN</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.3929</v>
+        <v>-1.1497</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7395</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9841</v>
+        <v>-0.902</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.3929</v>
+        <v>-1.1497</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.3929</v>
+        <v>-1.1497</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.3929</v>
+        <v>-1.1497</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.3929</v>
+        <v>-1.1497</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.3929</v>
+        <v>-1.1497</v>
       </c>
       <c r="N73" t="n">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74">
@@ -3814,7 +3814,7 @@
         <v>-0.7902</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0226</v>
+        <v>-1.0369</v>
       </c>
       <c r="E74" t="n">
         <v>-1.4884</v>
@@ -3860,7 +3860,7 @@
         <v>-0.9079</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1122</v>
+        <v>-1.1253</v>
       </c>
       <c r="E75" t="n">
         <v>-1.7102</v>
@@ -3906,7 +3906,7 @@
         <v>-0.9719</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1609</v>
+        <v>-1.1733</v>
       </c>
       <c r="E76" t="n">
         <v>-1.8307</v>
@@ -3952,7 +3952,7 @@
         <v>-0.9745</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1629</v>
+        <v>-1.1753</v>
       </c>
       <c r="E77" t="n">
         <v>-1.8357</v>
@@ -3998,7 +3998,7 @@
         <v>-0.9899</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1747</v>
+        <v>-1.1868</v>
       </c>
       <c r="E78" t="n">
         <v>-1.8647</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.304</v>
+        <v>-2.097</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.2232</v>
+        <v>-1.1133</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3521</v>
+        <v>-1.2794</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.304</v>
+        <v>-2.097</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.304</v>
+        <v>-2.097</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.304</v>
+        <v>-2.097</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.304</v>
+        <v>-2.097</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.304</v>
+        <v>-2.097</v>
       </c>
       <c r="N79" t="n">
         <v>205</v>
@@ -4090,7 +4090,7 @@
         <v>-1.5147</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.574</v>
+        <v>-1.5806</v>
       </c>
       <c r="E80" t="n">
         <v>-2.8532</v>
@@ -4136,7 +4136,7 @@
         <v>-1.9878</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.934</v>
+        <v>-1.9356</v>
       </c>
       <c r="E81" t="n">
         <v>-3.7443</v>
